--- a/src/test/resources/testData/organisation/stf/stf_organisation_empty_file.xlsx
+++ b/src/test/resources/testData/organisation/stf/stf_organisation_empty_file.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karthik.jaladurgam/workspace/securities-transfer-charge-submissions-ui-tests/src/test/resources/testData/organisation/stf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12C2F0F-384E-6641-A25B-53221A033CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F25F1BD-AE78-9F4F-9AC7-60D9AA4774FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
